--- a/ConfusionMatrices.xlsx
+++ b/ConfusionMatrices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattamor/MachineLearningProject_Group1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B30075-943D-BA4E-B817-5B80C58A64DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B9E840-E5EB-AA40-AD79-20FF0FEBA6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="1020" windowWidth="35860" windowHeight="17480" activeTab="1" xr2:uid="{70756974-4A70-6B43-AB54-573D8936E951}"/>
+    <workbookView xWindow="440" yWindow="1020" windowWidth="35860" windowHeight="17480" activeTab="4" xr2:uid="{70756974-4A70-6B43-AB54-573D8936E951}"/>
   </bookViews>
   <sheets>
     <sheet name="Tree" sheetId="3" r:id="rId1"/>
@@ -969,12 +969,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -982,13 +982,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB2490A-0D90-7843-B387-E7186D2304A2}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
@@ -996,7 +996,7 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="14" t="s">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D2" s="14"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="2">
@@ -1018,10 +1018,10 @@
       </c>
       <c r="G3">
         <f>2*(F4*F5)/(F4+F5)</f>
-        <v>0.35828219044191889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.45429604452355193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
@@ -1029,50 +1029,50 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>22383</v>
+        <v>44302</v>
       </c>
       <c r="D4" s="4">
-        <v>6469</v>
+        <v>11399</v>
       </c>
       <c r="F4" s="9">
         <f>1-D6</f>
-        <v>0.21909705456301298</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.29618424302296864</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="4">
-        <v>403</v>
+        <v>1158</v>
       </c>
       <c r="D5" s="3">
-        <v>1815</v>
+        <v>4797</v>
       </c>
       <c r="F5" s="9">
         <f>1-C6</f>
-        <v>0.98231370139559382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.97452705675318962</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C6" s="1">
         <f>C5/SUM(C4:C5)</f>
-        <v>1.7686298604406216E-2</v>
+        <v>2.5472943246810383E-2</v>
       </c>
       <c r="D6" s="1">
         <f>D4/SUM(D4:D5)</f>
-        <v>0.78090294543698702</v>
+        <v>0.70381575697703136</v>
       </c>
       <c r="E6" s="1">
         <f>(C5+D4)/SUM(C4:D5)</f>
-        <v>0.22117798519472159</v>
+        <v>0.2036622550927728</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>5</v>
       </c>
@@ -1081,19 +1081,39 @@
       </c>
       <c r="E7" s="9">
         <f>1-E6</f>
-        <v>0.77882201480527846</v>
+        <v>0.7963377449072272</v>
       </c>
       <c r="H7" s="11"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>44302</v>
+      </c>
+      <c r="L8">
+        <v>11399</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1158</v>
+      </c>
+      <c r="L9">
+        <v>4797</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="14" t="s">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="D10" s="14"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="8"/>
       <c r="C11" s="2">
@@ -1111,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>1</v>
       </c>
@@ -1129,7 +1149,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="2">
         <v>1</v>
@@ -1141,7 +1161,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1">
         <f>C13/SUM(C12:C13)</f>
         <v>7.7864293659621799E-3</v>
@@ -1158,7 +1178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
         <v>5</v>
       </c>
